--- a/AfterToken/Configs/GameConfig/Datas/player.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/player.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,20 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>maxStamina</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>staminaRecoveryRate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dodgeStaminaCost</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>moveSpeed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>dodgeSpeed</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dodgeDuration</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>rotationSpeed</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>colliderRadius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>prefab</t>
         </is>
@@ -471,20 +496,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -508,20 +558,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>最大体力</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>体力恢复速率</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>闪避消耗体力</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>移动速度</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>闪避速度</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>闪避持续时间</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>旋转速度</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>碰撞体半径</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>预制体</t>
         </is>
@@ -535,15 +610,30 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J4" t="n">
         <v>720</v>
       </c>
-      <c r="F4" t="n">
+      <c r="K4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Player_Hero</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/player.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/player.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,36 @@
           <t>prefab</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>weaponSwitchCooldown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>idleAnim</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>moveAnim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dodgeAnim</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>reloadAnim</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>deadAnim</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +569,36 @@
           <t>string</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -599,6 +659,36 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>预制体</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>武器切换冷却</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>待机动画名</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>移动动画名</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>闪避动画名</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>换弹动画名</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>死亡动画名</t>
         </is>
       </c>
     </row>
@@ -636,6 +726,34 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>Player_Hero</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Player_Idle</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Player_Run</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Player_Roll</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Player_Reload</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Player_Dead</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/player.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/player.xlsx
@@ -479,27 +479,27 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>idleAnim</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>moveAnim</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dodgeAnim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>reloadAnim</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>weaponSwitchCooldown</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>idleAnim</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>moveAnim</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dodgeAnim</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>reloadAnim</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>float</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>玩家ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>体力恢复速率</t>
+          <t>体力恢复速度</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>闪避消耗体力</t>
+          <t>闪避体力消耗</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -653,42 +653,42 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>碰撞体半径</t>
+          <t>碰撞半径</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>预制体</t>
+          <t>Prefab</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>待机动画</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>移动动画</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>闪避动画</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>换弹动画</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>武器切换冷却</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>待机动画名</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>移动动画名</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>闪避动画名</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>换弹动画名</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>死亡动画名</t>
+          <t>死亡动画</t>
         </is>
       </c>
     </row>
@@ -703,10 +703,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
@@ -718,42 +718,42 @@
         <v>0.4</v>
       </c>
       <c r="J4" t="n">
-        <v>720</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Player_Hero</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Idle</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Reload</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>0.3</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Player_Idle</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Player_Run</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Player_Roll</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Player_Reload</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Player_Dead</t>
+          <t>Dead</t>
         </is>
       </c>
     </row>
